--- a/questionnaire_templates/001_project_execution_readiness_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/001_project_execution_readiness_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey</t>
+          <t>project_execution_readiness_survey_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter project name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,107 +547,127 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_project</t>
+          <t>project_execution_readiness_survey_team_readiness</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_project</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Project Team Readiness</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Rate project team's readiness</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_team</t>
+          <t>project_execution_readiness_survey_launch_date</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_team</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Project Launch Date</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter project launch date</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_launch_date</t>
+          <t>project_execution_readiness_survey_launch_time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_launch_date</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Project Launch Time</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter project launch time</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_launch_time</t>
+          <t>project_execution_readiness_survey_status</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_launch_time</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Project Status</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select project status</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_status</t>
+          <t>project_execution_readiness_survey_comment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_status</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Project Comment</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter project comment</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,23 +677,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_comment</t>
+          <t>project_execution_readiness_survey_email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_comment</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Project Email</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enter project email</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_email</t>
+          <t>project_execution_readiness_survey_phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_email</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Project Phone</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enter project phone number</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,18 +736,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_phone</t>
+          <t>project_execution_readiness_survey_urgency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_phone</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Project Urgency</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rate project urgency</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +763,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_urgency</t>
+          <t>project_execution_readiness_survey_importance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_urgency</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Project Importance</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Rate project importance</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,38 +790,46 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_importance</t>
+          <t>project_execution_readiness_survey_confidence</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_importance</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Project Confidence</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Rate project confidence</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_confidence</t>
+          <t>project_execution_readiness_survey_comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_confidence</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Project Comments</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Enter project comments</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -791,46 +839,54 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_comments</t>
+          <t>project_execution_readiness_survey_confidence_level</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_comments</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Project Confidence Level</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Rate project confidence level</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_urgent</t>
+          <t>project_execution_readiness_survey_progress</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_urgent</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Project Progress</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Select project progress</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,15 +898,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_confident</t>
+          <t>project_execution_readiness_survey_status_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_confident</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Project Execution Readiness Survey Status 2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Select project status</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -860,43 +920,51 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_status</t>
+          <t>project_execution_readiness_survey_urgency_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_status</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Project Execution Readiness Survey Urgency 2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Rate project urgency</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_comments</t>
+          <t>project_execution_readiness_survey_importance_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_comments</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Project Execution Readiness Survey Importance 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Rate project importance</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -911,15 +979,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_urgency</t>
+          <t>project_execution_readiness_survey_confidence_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_urgency</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Project Execution Readiness Survey Confidence 2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Rate project confidence</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
@@ -929,20 +1001,24 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_importance</t>
+          <t>project_execution_readiness_survey_confidence_levels</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_importance</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Project Confidence Levels</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Select multiple confidence levels</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
@@ -957,131 +1033,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_confidence</t>
+          <t>project_execution_readiness_survey_confidence_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_confidence</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Project Execution Readiness Survey Confidence 3</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Rate project confidence</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>project_execution_readiness_survey_status</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>project_execution_readiness_survey_status</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>project_execution_readiness_survey_comments</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>project_execution_readiness_survey_comments</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>project_execution_readiness_survey_urgency</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>project_execution_readiness_survey_urgency</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>project_execution_readiness_survey_importance</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>project_execution_readiness_survey_importance</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>project_execution_readiness_survey_confidence</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>project_execution_readiness_survey_confidence</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +1063,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,255 +1091,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_team_choices</t>
+          <t>project_execution_readiness_survey_status_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'option_1'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Option 1'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_team_choices</t>
+          <t>project_execution_readiness_survey_status_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'option_2'}</t>
+          <t>delayed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Option 2'}</t>
+          <t>Delayed</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_team_choices</t>
+          <t>project_execution_readiness_survey_status_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'option_3'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Option 3'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_status_choices</t>
+          <t>project_execution_readiness_survey_progress_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'option_1',_'label':_'option_1'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Option 1', 'label': 'Option 1'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_status_choices</t>
+          <t>project_execution_readiness_survey_progress_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'option_2',_'label':_'option_2'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Option 2', 'label': 'Option 2'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_status_choices</t>
+          <t>project_execution_readiness_survey_progress_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'option_3',_'label':_'option_3'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Option 3', 'label': 'Option 3'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_urgent_choices</t>
+          <t>project_execution_readiness_survey_status_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'option_1'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Option 1'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_urgent_choices</t>
+          <t>project_execution_readiness_survey_status_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'option_2'}</t>
+          <t>delayed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Option 2'}</t>
+          <t>Delayed</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_urgent_choices</t>
+          <t>project_execution_readiness_survey_status_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'option_3'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Option 3'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_confident_choices</t>
+          <t>project_execution_readiness_survey_confidence_levels_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'option_1',_'label':_'option_1'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Option 1', 'label': 'Option 1'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_confident_choices</t>
+          <t>project_execution_readiness_survey_confidence_levels_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'option_2',_'label':_'option_2'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Option 2', 'label': 'Option 2'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>project_execution_readiness_survey_status_choices</t>
+          <t>project_execution_readiness_survey_confidence_levels_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'option_1',_'label':_'option_1'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Option 1', 'label': 'Option 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>project_execution_readiness_survey_status_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'value':_'option_2',_'label':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 2', 'label': 'Option 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>project_execution_readiness_survey_status_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'value':_'option_1',_'label':_'option_1'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 1', 'label': 'Option 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>project_execution_readiness_survey_status_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'value':_'option_2',_'label':_'option_2'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'value': 'Option 2', 'label': 'Option 2'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
